--- a/docs/03_DB설계서.xlsx
+++ b/docs/03_DB설계서.xlsx
@@ -105,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -127,11 +127,55 @@
         <color rgb="00CFE3F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -160,6 +204,8 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -554,6 +600,10 @@
           <t>DB설계서 (테이블 / 관계 / 저장방식)</t>
         </is>
       </c>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -563,9 +613,13 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
-        </is>
-      </c>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -578,6 +632,10 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -590,6 +648,10 @@
           <t>docs/DDL.sql, docs/seed.sql</t>
         </is>
       </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -602,6 +664,10 @@
           <t>SQLite (better-sqlite3, 오라클 VM 단일 파일)</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="11" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -702,7 +768,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>id(PK), email(UQ), password_hash(bcrypt), name, verified(0/1), verify_token, created_at</t>
+          <t>id(PK), email(UQ), password_hash(bcrypt), name, verified(0/1), verify_token, reset_token, reset_expires, created_at</t>
         </is>
       </c>
     </row>
@@ -743,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -826,6 +892,18 @@
       <c r="B7" s="7" t="inlineStr">
         <is>
           <t>날씨·추천·상품은 외부 API라 DB에 저장하지 않음. 캐시는 메모리(날씨 프록시)·localStorage(추천)에만</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>DEC-DB-06</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정 — users.reset_token/reset_expires 컬럼(1시간 만료·1회용). 탈퇴는 users+user_data 트랜잭션 삭제(FK CASCADE 미신뢰, 명시 삭제)</t>
         </is>
       </c>
     </row>
@@ -844,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -893,6 +971,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>users에 reset_token·reset_expires 추가(비밀번호 재설정), DEC-DB-06 기록. DDL.sql 동기화</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">
